--- a/database/event/6140/event_6140_evp_summary.xlsx
+++ b/database/event/6140/event_6140_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.506</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4367</v>
+        <v>2.3747</v>
       </c>
       <c r="E2" t="n">
         <v>7.0747</v>
@@ -548,7 +548,7 @@
         <v>4.3048</v>
       </c>
       <c r="D3" t="n">
-        <v>2.309</v>
+        <v>2.2488</v>
       </c>
       <c r="E3" t="n">
         <v>6.7587</v>
@@ -594,7 +594,7 @@
         <v>4.2482</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2731</v>
+        <v>2.2134</v>
       </c>
       <c r="E4" t="n">
         <v>6.6699</v>
@@ -640,7 +640,7 @@
         <v>3.8625</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0285</v>
+        <v>1.9721</v>
       </c>
       <c r="E5" t="n">
         <v>6.0644</v>
@@ -686,7 +686,7 @@
         <v>3.6754</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9098</v>
+        <v>1.8551</v>
       </c>
       <c r="E6" t="n">
         <v>5.7706</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.5108</v>
+        <v>5.4754</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5099</v>
+        <v>3.4874</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8049</v>
+        <v>1.7375</v>
       </c>
       <c r="E7" t="n">
-        <v>5.5108</v>
+        <v>5.4754</v>
       </c>
       <c r="F7" t="n">
-        <v>4.6434</v>
+        <v>4.608</v>
       </c>
       <c r="G7" t="n">
         <v>0.8673999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9778</v>
+        <v>4.9223</v>
       </c>
       <c r="I7" t="n">
         <v>5.0476</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.2062</v>
+        <v>5.194</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3159</v>
+        <v>3.3082</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6818</v>
+        <v>1.6254</v>
       </c>
       <c r="E8" t="n">
-        <v>5.2062</v>
+        <v>5.194</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2742</v>
+        <v>3.262</v>
       </c>
       <c r="G8" t="n">
         <v>1.932</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2742</v>
+        <v>3.262</v>
       </c>
       <c r="I8" t="n">
         <v>3.2894</v>
@@ -824,7 +824,7 @@
         <v>3.2232</v>
       </c>
       <c r="D9" t="n">
-        <v>1.623</v>
+        <v>1.5722</v>
       </c>
       <c r="E9" t="n">
         <v>5.0606</v>
@@ -870,7 +870,7 @@
         <v>2.7618</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3303</v>
+        <v>1.2836</v>
       </c>
       <c r="E10" t="n">
         <v>4.3361</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.2222</v>
+        <v>4.1911</v>
       </c>
       <c r="C11" t="n">
-        <v>2.6892</v>
+        <v>2.6694</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2843</v>
+        <v>1.2258</v>
       </c>
       <c r="E11" t="n">
-        <v>4.2222</v>
+        <v>4.1911</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2571</v>
+        <v>4.226</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0349</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3721</v>
+        <v>4.3233</v>
       </c>
       <c r="I11" t="n">
         <v>4.4334</v>
@@ -962,7 +962,7 @@
         <v>2.3968</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0988</v>
+        <v>1.0553</v>
       </c>
       <c r="E12" t="n">
         <v>3.7631</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.6113</v>
+        <v>3.5761</v>
       </c>
       <c r="C13" t="n">
-        <v>2.3001</v>
+        <v>2.2777</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0375</v>
+        <v>0.9808</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6113</v>
+        <v>3.5761</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1584</v>
+        <v>3.1232</v>
       </c>
       <c r="G13" t="n">
         <v>0.4529</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1584</v>
+        <v>3.1232</v>
       </c>
       <c r="I13" t="n">
         <v>3.2027</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.5666</v>
+        <v>3.5238</v>
       </c>
       <c r="C14" t="n">
-        <v>2.2716</v>
+        <v>2.2444</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0195</v>
+        <v>0.96</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5666</v>
+        <v>3.5238</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8447</v>
+        <v>3.8019</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2781</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8447</v>
+        <v>3.8019</v>
       </c>
       <c r="I14" t="n">
         <v>3.8987</v>
@@ -1100,7 +1100,7 @@
         <v>2.2408</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9999</v>
+        <v>0.9577</v>
       </c>
       <c r="E15" t="n">
         <v>3.5181</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9702</v>
+        <v>2.9591</v>
       </c>
       <c r="C16" t="n">
-        <v>1.8918</v>
+        <v>1.8847</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7785</v>
+        <v>0.735</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9702</v>
+        <v>2.9591</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9702</v>
+        <v>2.9591</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9702</v>
+        <v>2.9591</v>
       </c>
       <c r="I16" t="n">
         <v>2.984</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8751</v>
+        <v>2.8429</v>
       </c>
       <c r="C17" t="n">
-        <v>1.8312</v>
+        <v>1.8107</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7401</v>
+        <v>0.6887</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8751</v>
+        <v>2.8429</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8878</v>
+        <v>2.8556</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0127</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8878</v>
+        <v>2.8556</v>
       </c>
       <c r="I17" t="n">
         <v>2.9283</v>
@@ -1238,7 +1238,7 @@
         <v>1.7643</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6977</v>
+        <v>0.6597</v>
       </c>
       <c r="E18" t="n">
         <v>2.7701</v>
@@ -1284,7 +1284,7 @@
         <v>1.7567</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6928</v>
+        <v>0.6549</v>
       </c>
       <c r="E19" t="n">
         <v>2.7581</v>
@@ -1330,7 +1330,7 @@
         <v>1.6747</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6408</v>
+        <v>0.6036</v>
       </c>
       <c r="E20" t="n">
         <v>2.6293</v>
@@ -1376,7 +1376,7 @@
         <v>1.6422</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6203</v>
+        <v>0.5833</v>
       </c>
       <c r="E21" t="n">
         <v>2.5784</v>
@@ -1422,7 +1422,7 @@
         <v>1.5944</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5899</v>
+        <v>0.5534</v>
       </c>
       <c r="E22" t="n">
         <v>2.5033</v>
@@ -1468,7 +1468,7 @@
         <v>1.4996</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5298</v>
+        <v>0.4941</v>
       </c>
       <c r="E23" t="n">
         <v>2.3545</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3275</v>
+        <v>2.318</v>
       </c>
       <c r="C24" t="n">
-        <v>1.4824</v>
+        <v>1.4764</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5189</v>
+        <v>0.4796</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3275</v>
+        <v>2.318</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5677</v>
+        <v>2.5582</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2402</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5677</v>
+        <v>2.5582</v>
       </c>
       <c r="I24" t="n">
         <v>2.5797</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.3103</v>
+        <v>2.2744</v>
       </c>
       <c r="C25" t="n">
-        <v>1.4715</v>
+        <v>1.4486</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5119</v>
+        <v>0.4622</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3103</v>
+        <v>2.2744</v>
       </c>
       <c r="F25" t="n">
-        <v>3.2204</v>
+        <v>3.1845</v>
       </c>
       <c r="G25" t="n">
         <v>-0.9101</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2204</v>
+        <v>3.1845</v>
       </c>
       <c r="I25" t="n">
         <v>3.2656</v>
@@ -1606,7 +1606,7 @@
         <v>1.3007</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4036</v>
+        <v>0.3697</v>
       </c>
       <c r="E26" t="n">
         <v>2.0421</v>
@@ -1652,7 +1652,7 @@
         <v>1.2633</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3799</v>
+        <v>0.3463</v>
       </c>
       <c r="E27" t="n">
         <v>1.9834</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5727</v>
+        <v>1.5647</v>
       </c>
       <c r="C28" t="n">
-        <v>1.0017</v>
+        <v>0.9966</v>
       </c>
       <c r="D28" t="n">
-        <v>0.214</v>
+        <v>0.1795</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5727</v>
+        <v>1.5647</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7195</v>
+        <v>0.7115</v>
       </c>
       <c r="G28" t="n">
         <v>0.8532</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7195</v>
+        <v>0.7115</v>
       </c>
       <c r="I28" t="n">
         <v>0.7296</v>
@@ -1744,7 +1744,7 @@
         <v>0.9709</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1944</v>
+        <v>0.1634</v>
       </c>
       <c r="E29" t="n">
         <v>1.5243</v>
@@ -1790,7 +1790,7 @@
         <v>0.9628</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1893</v>
+        <v>0.1584</v>
       </c>
       <c r="E30" t="n">
         <v>1.5117</v>
@@ -1836,7 +1836,7 @@
         <v>0.9536</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1835</v>
+        <v>0.1526</v>
       </c>
       <c r="E31" t="n">
         <v>1.4972</v>
@@ -1882,7 +1882,7 @@
         <v>0.9337</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1708</v>
+        <v>0.1401</v>
       </c>
       <c r="E32" t="n">
         <v>1.4659</v>
@@ -1928,7 +1928,7 @@
         <v>0.8328</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1068</v>
+        <v>0.077</v>
       </c>
       <c r="E33" t="n">
         <v>1.3075</v>
@@ -1974,7 +1974,7 @@
         <v>0.716</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0328</v>
+        <v>0.004</v>
       </c>
       <c r="E34" t="n">
         <v>1.1242</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9887</v>
+        <v>0.985</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6297</v>
+        <v>0.6274</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0219</v>
+        <v>-0.0515</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9887</v>
+        <v>0.985</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0075</v>
+        <v>1.0038</v>
       </c>
       <c r="G35" t="n">
         <v>-0.0188</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0075</v>
+        <v>1.0038</v>
       </c>
       <c r="I35" t="n">
         <v>1.0122</v>
@@ -2066,7 +2066,7 @@
         <v>0.6192</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0287</v>
+        <v>-0.0566</v>
       </c>
       <c r="E36" t="n">
         <v>0.9721</v>
@@ -2112,7 +2112,7 @@
         <v>0.5407</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0784</v>
+        <v>-0.1057</v>
       </c>
       <c r="E37" t="n">
         <v>0.8489</v>
@@ -2158,7 +2158,7 @@
         <v>0.5043</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1015</v>
+        <v>-0.1285</v>
       </c>
       <c r="E38" t="n">
         <v>0.7917</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5604</v>
+        <v>0.5583</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3569</v>
+        <v>0.3556</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.195</v>
+        <v>-0.2215</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5604</v>
+        <v>0.5583</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5604</v>
+        <v>0.5583</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5604</v>
+        <v>0.5583</v>
       </c>
       <c r="I39" t="n">
         <v>0.5629999999999999</v>
@@ -2250,7 +2250,7 @@
         <v>0.2676</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2516</v>
+        <v>-0.2765</v>
       </c>
       <c r="E40" t="n">
         <v>0.4202</v>
@@ -2296,7 +2296,7 @@
         <v>0.2075</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2897</v>
+        <v>-0.3141</v>
       </c>
       <c r="E41" t="n">
         <v>0.3258</v>
@@ -2342,7 +2342,7 @@
         <v>0.1368</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3346</v>
+        <v>-0.3583</v>
       </c>
       <c r="E42" t="n">
         <v>0.2148</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1399</v>
+        <v>0.1393</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0891</v>
+        <v>0.0887</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3648</v>
+        <v>-0.3884</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1399</v>
+        <v>0.1393</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1399</v>
+        <v>0.1393</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1399</v>
+        <v>0.1393</v>
       </c>
       <c r="I43" t="n">
         <v>0.1405</v>
@@ -2434,7 +2434,7 @@
         <v>0.0799</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3707</v>
+        <v>-0.3939</v>
       </c>
       <c r="E44" t="n">
         <v>0.1255</v>
@@ -2480,7 +2480,7 @@
         <v>-0.0935</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4807</v>
+        <v>-0.5024</v>
       </c>
       <c r="E45" t="n">
         <v>-0.1468</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.2044</v>
+        <v>-0.2037</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1302</v>
+        <v>-0.1297</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5039</v>
+        <v>-0.5251</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.2044</v>
+        <v>-0.2037</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0641</v>
+        <v>-0.0634</v>
       </c>
       <c r="G46" t="n">
         <v>-0.1403</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0641</v>
+        <v>-0.0634</v>
       </c>
       <c r="I46" t="n">
         <v>-0.065</v>
@@ -2572,7 +2572,7 @@
         <v>-0.166</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.5478</v>
       </c>
       <c r="E47" t="n">
         <v>-0.2607</v>
@@ -2618,7 +2618,7 @@
         <v>-0.2102</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5547</v>
+        <v>-0.5754</v>
       </c>
       <c r="E48" t="n">
         <v>-0.33</v>
@@ -2664,7 +2664,7 @@
         <v>-0.2225</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5625</v>
+        <v>-0.5831</v>
       </c>
       <c r="E49" t="n">
         <v>-0.3493</v>
@@ -2710,7 +2710,7 @@
         <v>-0.2315</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5682</v>
+        <v>-0.5887</v>
       </c>
       <c r="E50" t="n">
         <v>-0.3634</v>
@@ -2756,7 +2756,7 @@
         <v>-0.2349</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5703</v>
+        <v>-0.5908</v>
       </c>
       <c r="E51" t="n">
         <v>-0.3688</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.4129</v>
+        <v>-0.4086</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.263</v>
+        <v>-0.2602</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.6067</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.4129</v>
+        <v>-0.4086</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.1554</v>
+        <v>-1.1511</v>
       </c>
       <c r="G52" t="n">
         <v>0.7425</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.1554</v>
+        <v>-1.1511</v>
       </c>
       <c r="I52" t="n">
         <v>-1.1608</v>
@@ -2848,7 +2848,7 @@
         <v>-0.3954</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6722</v>
+        <v>-0.6912</v>
       </c>
       <c r="E53" t="n">
         <v>-0.6208</v>
@@ -2894,7 +2894,7 @@
         <v>-0.4108</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6819</v>
+        <v>-0.7009</v>
       </c>
       <c r="E54" t="n">
         <v>-0.645</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.7111</v>
+        <v>-0.7056</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4529</v>
+        <v>-0.4494</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7086</v>
+        <v>-0.725</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.7111</v>
+        <v>-0.7056</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4931</v>
+        <v>-0.4876</v>
       </c>
       <c r="G55" t="n">
         <v>-0.218</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4931</v>
+        <v>-0.4876</v>
       </c>
       <c r="I55" t="n">
         <v>-0.5</v>
@@ -2986,7 +2986,7 @@
         <v>-0.4589</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7124</v>
+        <v>-0.731</v>
       </c>
       <c r="E56" t="n">
         <v>-0.7205</v>
@@ -3032,7 +3032,7 @@
         <v>-0.5415</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7648</v>
+        <v>-0.7826</v>
       </c>
       <c r="E57" t="n">
         <v>-0.8502</v>
@@ -3078,7 +3078,7 @@
         <v>-0.5474</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.7863</v>
       </c>
       <c r="E58" t="n">
         <v>-0.8595</v>
@@ -3124,7 +3124,7 @@
         <v>-0.5517</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7713</v>
+        <v>-0.789</v>
       </c>
       <c r="E59" t="n">
         <v>-0.8662</v>
@@ -3170,7 +3170,7 @@
         <v>-0.5854</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7927</v>
+        <v>-0.8101</v>
       </c>
       <c r="E60" t="n">
         <v>-0.9191</v>
@@ -3216,7 +3216,7 @@
         <v>-0.663</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8419</v>
+        <v>-0.8586</v>
       </c>
       <c r="E61" t="n">
         <v>-1.041</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.0676</v>
+        <v>-1.0636</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.68</v>
+        <v>-0.6774</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8526</v>
+        <v>-0.8676</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.0676</v>
+        <v>-1.0636</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.0676</v>
+        <v>-1.0636</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-1.0676</v>
+        <v>-1.0636</v>
       </c>
       <c r="I62" t="n">
         <v>-1.0726</v>
@@ -3308,7 +3308,7 @@
         <v>-0.7225</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8796</v>
+        <v>-0.8958</v>
       </c>
       <c r="E63" t="n">
         <v>-1.1343</v>
@@ -3354,7 +3354,7 @@
         <v>-0.728</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8831</v>
+        <v>-0.8993</v>
       </c>
       <c r="E64" t="n">
         <v>-1.143</v>
@@ -3400,7 +3400,7 @@
         <v>-0.7582</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9023</v>
+        <v>-0.9182</v>
       </c>
       <c r="E65" t="n">
         <v>-1.1904</v>
@@ -3446,7 +3446,7 @@
         <v>-0.7821</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9174</v>
+        <v>-0.9331</v>
       </c>
       <c r="E66" t="n">
         <v>-1.2279</v>
@@ -3492,7 +3492,7 @@
         <v>-0.7863</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9201</v>
+        <v>-0.9358</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2346</v>
@@ -3538,7 +3538,7 @@
         <v>-0.7935</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9247</v>
+        <v>-0.9403</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2459</v>
@@ -3584,7 +3584,7 @@
         <v>-0.8332000000000001</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9498</v>
+        <v>-0.9651</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3081</v>
@@ -3630,7 +3630,7 @@
         <v>-0.8351</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.951</v>
+        <v>-0.9663</v>
       </c>
       <c r="E70" t="n">
         <v>-1.3111</v>
@@ -3666,93 +3666,93 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.3531</v>
+        <v>-1.3522</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.8618</v>
+        <v>-0.8612</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.968</v>
+        <v>-0.9826</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.3531</v>
+        <v>-1.3522</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.3531</v>
+        <v>-1.0786</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>-0.2736</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.3531</v>
+        <v>-1.0786</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.3531</v>
+        <v>-1.0877</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>-0.2736</v>
       </c>
       <c r="K71" t="n">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.3531</v>
+        <v>-1.3613</v>
       </c>
       <c r="N71" t="n">
-        <v>230</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3563</v>
+        <v>-1.3531</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.8639</v>
+        <v>-0.8618</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.983</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3563</v>
+        <v>-1.3531</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.0827</v>
+        <v>-1.3531</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.2736</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.0827</v>
+        <v>-1.3531</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.0877</v>
+        <v>-1.3531</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.2736</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="L72" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.3613</v>
+        <v>-1.3531</v>
       </c>
       <c r="N72" t="n">
-        <v>334</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73">
@@ -3768,7 +3768,7 @@
         <v>-0.8781</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.9931</v>
       </c>
       <c r="E73" t="n">
         <v>-1.3786</v>
@@ -3814,7 +3814,7 @@
         <v>-1.0367</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0789</v>
+        <v>-1.0923</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6276</v>
@@ -3860,7 +3860,7 @@
         <v>-1.0916</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1137</v>
+        <v>-1.1267</v>
       </c>
       <c r="E75" t="n">
         <v>-1.7138</v>
@@ -3906,7 +3906,7 @@
         <v>-1.14</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1444</v>
+        <v>-1.157</v>
       </c>
       <c r="E76" t="n">
         <v>-1.7899</v>
@@ -3952,7 +3952,7 @@
         <v>-1.2235</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1974</v>
+        <v>-1.2092</v>
       </c>
       <c r="E77" t="n">
         <v>-1.921</v>
@@ -3998,7 +3998,7 @@
         <v>-1.3528</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2794</v>
+        <v>-1.2901</v>
       </c>
       <c r="E78" t="n">
         <v>-2.124</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.7618</v>
+        <v>-2.7515</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.759</v>
+        <v>-1.7525</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5371</v>
+        <v>-1.5401</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.7618</v>
+        <v>-2.7515</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.7618</v>
+        <v>-2.7515</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.7618</v>
+        <v>-2.7515</v>
       </c>
       <c r="I79" t="n">
         <v>-2.7747</v>
@@ -4090,7 +4090,7 @@
         <v>-1.9004</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6267</v>
+        <v>-1.6326</v>
       </c>
       <c r="E80" t="n">
         <v>-2.9837</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.243</v>
+        <v>-3.2164</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.0655</v>
+        <v>-2.0486</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7315</v>
+        <v>-1.7253</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.243</v>
+        <v>-3.2164</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.3874</v>
+        <v>-2.3608</v>
       </c>
       <c r="G81" t="n">
         <v>-0.8556</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.3874</v>
+        <v>-2.3608</v>
       </c>
       <c r="I81" t="n">
         <v>-2.4209</v>
